--- a/_stats_outputs/anova_coefs.xlsx
+++ b/_stats_outputs/anova_coefs.xlsx
@@ -416,7 +416,7 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>985.8468240498761</v>
+        <v>985.846824049876</v>
       </c>
       <c r="D2">
         <v>1002.723216088297</v>
@@ -425,7 +425,7 @@
         <v>-487.923412024938</v>
       </c>
       <c r="F2">
-        <v>975.8468240498761</v>
+        <v>975.846824049876</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -497,16 +497,16 @@
         <v>5</v>
       </c>
       <c r="C5">
-        <v>1213.12375180456</v>
+        <v>1213.123751804559</v>
       </c>
       <c r="D5">
-        <v>1230.000143842981</v>
+        <v>1230.00014384298</v>
       </c>
       <c r="E5">
-        <v>-601.5618759022801</v>
+        <v>-601.5618759022797</v>
       </c>
       <c r="F5">
-        <v>1203.12375180456</v>
+        <v>1203.123751804559</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -524,16 +524,16 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>1228.2914983683</v>
+        <v>1228.291498368299</v>
       </c>
       <c r="D6">
-        <v>1245.167890406721</v>
+        <v>1245.16789040672</v>
       </c>
       <c r="E6">
-        <v>-609.1457491841498</v>
+        <v>-609.1457491841497</v>
       </c>
       <c r="F6">
-        <v>1218.2914983683</v>
+        <v>1218.291498368299</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -551,16 +551,16 @@
         <v>5</v>
       </c>
       <c r="C7">
-        <v>1340.794040975441</v>
+        <v>1340.794040975439</v>
       </c>
       <c r="D7">
-        <v>1357.670433013861</v>
+        <v>1357.67043301386</v>
       </c>
       <c r="E7">
-        <v>-665.3970204877203</v>
+        <v>-665.3970204877197</v>
       </c>
       <c r="F7">
-        <v>1330.794040975441</v>
+        <v>1330.794040975439</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -578,7 +578,7 @@
         <v>13</v>
       </c>
       <c r="C8">
-        <v>977.2451026966708</v>
+        <v>977.2451026966709</v>
       </c>
       <c r="D8">
         <v>1021.123721996565</v>
@@ -587,16 +587,16 @@
         <v>-475.6225513483354</v>
       </c>
       <c r="F8">
-        <v>951.2451026966708</v>
+        <v>951.2451026966709</v>
       </c>
       <c r="G8">
-        <v>24.60172135320533</v>
+        <v>24.60172135320511</v>
       </c>
       <c r="H8">
         <v>8</v>
       </c>
       <c r="I8">
-        <v>0.001815338801277888</v>
+        <v>0.001815338801278049</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -686,25 +686,25 @@
         <v>13</v>
       </c>
       <c r="C11">
-        <v>1146.335347681105</v>
+        <v>1146.335347681106</v>
       </c>
       <c r="D11">
-        <v>1190.213966980999</v>
+        <v>1190.213966981</v>
       </c>
       <c r="E11">
-        <v>-560.1676738405527</v>
+        <v>-560.1676738405528</v>
       </c>
       <c r="F11">
-        <v>1120.335347681105</v>
+        <v>1120.335347681106</v>
       </c>
       <c r="G11">
-        <v>82.78840412345494</v>
+        <v>82.7884041234538</v>
       </c>
       <c r="H11">
         <v>8</v>
       </c>
       <c r="I11">
-        <v>1.340387312208153E-14</v>
+        <v>1.34038731220886E-14</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -722,25 +722,25 @@
         <v>13</v>
       </c>
       <c r="C12">
-        <v>1213.543465391333</v>
+        <v>1213.543465391334</v>
       </c>
       <c r="D12">
         <v>1257.422084691228</v>
       </c>
       <c r="E12">
-        <v>-593.7717326956667</v>
+        <v>-593.7717326956669</v>
       </c>
       <c r="F12">
-        <v>1187.543465391333</v>
+        <v>1187.543465391334</v>
       </c>
       <c r="G12">
-        <v>30.74803297696621</v>
+        <v>30.74803297696576</v>
       </c>
       <c r="H12">
         <v>8</v>
       </c>
       <c r="I12">
-        <v>0.0001557729588085939</v>
+        <v>0.000155772958808623</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -770,13 +770,13 @@
         <v>1293.398499994539</v>
       </c>
       <c r="G13">
-        <v>37.39554098090161</v>
+        <v>37.39554098090048</v>
       </c>
       <c r="H13">
         <v>8</v>
       </c>
       <c r="I13">
-        <v>9.732383090407838E-06</v>
+        <v>9.732383090412531E-06</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
